--- a/data/trans_orig/IP18B-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP18B-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3706</t>
+          <t>3892</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12232</t>
+          <t>12239</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,7 +748,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4285</t>
+          <t>4772</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13921</t>
+          <t>13866</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>10128</t>
+          <t>9799</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>22534</t>
+          <t>22580</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,21%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>70120</t>
+          <t>70124</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>86242</t>
+          <t>86325</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>74,64%</t>
+          <t>74,71%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>73912</t>
+          <t>73658</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>90783</t>
+          <t>91373</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>57,03%</t>
+          <t>56,83%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>70,05%</t>
+          <t>70,5%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>149363</t>
+          <t>149278</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>172975</t>
+          <t>172031</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>60,93%</t>
+          <t>60,89%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>70,56%</t>
+          <t>70,18%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>22534</t>
+          <t>22039</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>37420</t>
+          <t>37467</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>32,39%</t>
+          <t>32,43%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>30695</t>
+          <t>29920</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>46763</t>
+          <t>47165</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>23,68%</t>
+          <t>23,09%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>36,08%</t>
+          <t>36,39%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>58579</t>
+          <t>58722</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>80139</t>
+          <t>79499</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>23,9%</t>
+          <t>23,95%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>32,69%</t>
+          <t>32,43%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>6681</t>
+          <t>6227</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>16253</t>
+          <t>16337</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>9869</t>
+          <t>9779</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>21366</t>
+          <t>21895</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>18576</t>
+          <t>19071</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>34104</t>
+          <t>35458</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>10,21%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>105123</t>
+          <t>104436</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>123490</t>
+          <t>123086</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>63,33%</t>
+          <t>62,92%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>74,39%</t>
+          <t>74,15%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>127927</t>
+          <t>129110</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>146845</t>
+          <t>146730</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>70,56%</t>
+          <t>71,21%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>80,99%</t>
+          <t>80,93%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>239659</t>
+          <t>238803</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>265104</t>
+          <t>264617</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>69,01%</t>
+          <t>68,76%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>76,33%</t>
+          <t>76,19%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>32230</t>
+          <t>32911</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>49614</t>
+          <t>50533</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>19,83%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>29,89%</t>
+          <t>30,44%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>21114</t>
+          <t>21531</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>36051</t>
+          <t>36190</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>19,96%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>56999</t>
+          <t>57623</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>80914</t>
+          <t>81070</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>23,34%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4444</t>
+          <t>4584</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>13000</t>
+          <t>12623</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>2091</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>9859</t>
+          <t>8761</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>7981</t>
+          <t>8348</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>18601</t>
+          <t>18752</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,26%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>93259</t>
+          <t>93234</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>107082</t>
+          <t>106923</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>74,86%</t>
+          <t>74,84%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>85,96%</t>
+          <t>85,83%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>102596</t>
+          <t>101683</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>116504</t>
+          <t>116339</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>76,68%</t>
+          <t>76,0%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>87,08%</t>
+          <t>86,95%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>200113</t>
+          <t>200227</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>219931</t>
+          <t>219428</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>77,45%</t>
+          <t>77,5%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>85,12%</t>
+          <t>84,93%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>10924</t>
+          <t>11108</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>22459</t>
+          <t>22674</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>13231</t>
+          <t>12814</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>26178</t>
+          <t>26278</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>19,64%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>26494</t>
+          <t>27285</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>44987</t>
+          <t>44261</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>17,13%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5343</t>
+          <t>5344</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15852</t>
+          <t>16817</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2121,7 +2121,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3270</t>
+          <t>3300</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>11810</t>
+          <t>11155</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>10056</t>
+          <t>10604</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>23504</t>
+          <t>24021</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,43%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>143500</t>
+          <t>142983</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>162565</t>
+          <t>161954</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>74,53%</t>
+          <t>74,26%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>84,43%</t>
+          <t>84,11%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>130064</t>
+          <t>128930</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>147122</t>
+          <t>147645</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>71,74%</t>
+          <t>71,11%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>81,15%</t>
+          <t>81,43%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>278607</t>
+          <t>278089</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>305324</t>
+          <t>304575</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>74,52%</t>
+          <t>74,39%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>81,67%</t>
+          <t>81,47%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>21466</t>
+          <t>20768</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>38985</t>
+          <t>38407</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>19,95%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>28731</t>
+          <t>28315</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>44923</t>
+          <t>45173</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>15,62%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>24,78%</t>
+          <t>24,92%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>53744</t>
+          <t>54010</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>78040</t>
+          <t>78637</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>21,03%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>26487</t>
+          <t>27068</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>44683</t>
+          <t>45931</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>26671</t>
+          <t>25496</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>44963</t>
+          <t>44729</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>57599</t>
+          <t>58166</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>83626</t>
+          <t>84562</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,9%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>429210</t>
+          <t>429125</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>464163</t>
+          <t>462620</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>71,7%</t>
+          <t>71,68%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>77,53%</t>
+          <t>77,28%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>452444</t>
+          <t>450040</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>484936</t>
+          <t>486568</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>72,27%</t>
+          <t>71,89%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>77,46%</t>
+          <t>77,73%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>891477</t>
+          <t>889736</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>940898</t>
+          <t>941094</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>72,79%</t>
+          <t>72,65%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>76,83%</t>
+          <t>76,84%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>100459</t>
+          <t>100758</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>132024</t>
+          <t>131838</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>22,05%</t>
+          <t>22,02%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>107051</t>
+          <t>106322</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>138754</t>
+          <t>138219</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>16,98%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>22,08%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>215314</t>
+          <t>215505</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>262744</t>
+          <t>260096</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>21,45%</t>
+          <t>21,24%</t>
         </is>
       </c>
     </row>
@@ -3245,12 +3245,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5015</t>
+          <t>5333</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15339</t>
+          <t>15401</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3260,12 +3260,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2696</t>
+          <t>2309</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12381</t>
+          <t>11203</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3295,12 +3295,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>9898</t>
+          <t>9751</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>23612</t>
+          <t>22867</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3330,12 +3330,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,21%</t>
         </is>
       </c>
     </row>
@@ -3358,12 +3358,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>80783</t>
+          <t>81239</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>99684</t>
+          <t>98901</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3373,12 +3373,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>61,44%</t>
+          <t>61,79%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>75,82%</t>
+          <t>75,22%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3393,12 +3393,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>92620</t>
+          <t>93256</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>111759</t>
+          <t>111461</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3408,12 +3408,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>63,03%</t>
+          <t>63,47%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>76,06%</t>
+          <t>75,85%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3428,12 +3428,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>180010</t>
+          <t>180737</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>206502</t>
+          <t>206923</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3443,12 +3443,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>64,66%</t>
+          <t>64,92%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>74,17%</t>
+          <t>74,32%</t>
         </is>
       </c>
     </row>
@@ -3471,12 +3471,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>22980</t>
+          <t>23458</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>39846</t>
+          <t>40222</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3486,12 +3486,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>30,31%</t>
+          <t>30,59%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3506,12 +3506,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>30166</t>
+          <t>30347</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>47961</t>
+          <t>47753</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>20,65%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>32,64%</t>
+          <t>32,5%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3541,12 +3541,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>57634</t>
+          <t>58600</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>82443</t>
+          <t>83000</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3556,12 +3556,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>21,05%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>29,61%</t>
+          <t>29,81%</t>
         </is>
       </c>
     </row>
@@ -3701,12 +3701,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>6605</t>
+          <t>6441</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>16936</t>
+          <t>16354</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3716,12 +3716,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>10599</t>
+          <t>10012</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>22619</t>
+          <t>22722</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3751,12 +3751,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>18998</t>
+          <t>19258</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>34926</t>
+          <t>35772</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3786,12 +3786,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,89%</t>
         </is>
       </c>
     </row>
@@ -3814,12 +3814,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>144227</t>
+          <t>144103</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>161761</t>
+          <t>162574</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3829,12 +3829,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>74,65%</t>
+          <t>74,58%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>83,72%</t>
+          <t>84,14%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>149989</t>
+          <t>150104</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>170180</t>
+          <t>169757</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3864,12 +3864,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>71,74%</t>
+          <t>71,79%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>81,4%</t>
+          <t>81,19%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>299221</t>
+          <t>301007</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>325796</t>
+          <t>326499</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3899,12 +3899,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>74,38%</t>
+          <t>74,82%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>80,98%</t>
+          <t>81,16%</t>
         </is>
       </c>
     </row>
@@ -3927,12 +3927,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>21671</t>
+          <t>21494</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>37477</t>
+          <t>36944</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3942,12 +3942,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>19,12%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>25264</t>
+          <t>24510</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>42749</t>
+          <t>42549</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3977,12 +3977,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>20,35%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>50866</t>
+          <t>51147</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>73935</t>
+          <t>73554</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4012,12 +4012,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>18,28%</t>
         </is>
       </c>
     </row>
@@ -4157,12 +4157,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3425</t>
+          <t>3223</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>12037</t>
+          <t>11300</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4172,12 +4172,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>7886</t>
+          <t>7752</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>18699</t>
+          <t>19653</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4207,12 +4207,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>13216</t>
+          <t>12470</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>27013</t>
+          <t>27492</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4242,12 +4242,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>9,21%</t>
         </is>
       </c>
     </row>
@@ -4270,12 +4270,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>105427</t>
+          <t>105298</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>120586</t>
+          <t>120992</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4285,12 +4285,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>73,93%</t>
+          <t>73,84%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>84,56%</t>
+          <t>84,85%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>119625</t>
+          <t>120288</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>134760</t>
+          <t>135202</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4320,12 +4320,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>76,72%</t>
+          <t>77,14%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>86,42%</t>
+          <t>86,71%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>230296</t>
+          <t>230652</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>252947</t>
+          <t>252064</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4355,12 +4355,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>77,14%</t>
+          <t>77,26%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>84,73%</t>
+          <t>84,44%</t>
         </is>
       </c>
     </row>
@@ -4383,12 +4383,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>16219</t>
+          <t>15229</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>29635</t>
+          <t>29493</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4398,12 +4398,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>20,68%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>10545</t>
+          <t>10396</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>22417</t>
+          <t>22099</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>14,17%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>29021</t>
+          <t>29192</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>47014</t>
+          <t>47280</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>15,84%</t>
         </is>
       </c>
     </row>
@@ -4613,12 +4613,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4369</t>
+          <t>4063</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14312</t>
+          <t>13944</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4628,12 +4628,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4648,12 +4648,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>10824</t>
+          <t>11364</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>24155</t>
+          <t>24571</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4663,12 +4663,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4683,12 +4683,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>18014</t>
+          <t>17995</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>34787</t>
+          <t>34468</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4698,12 +4698,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,43%</t>
         </is>
       </c>
     </row>
@@ -4726,12 +4726,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>157976</t>
+          <t>158815</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>177195</t>
+          <t>177130</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4741,12 +4741,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>77,7%</t>
+          <t>78,11%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>87,15%</t>
+          <t>87,12%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4761,12 +4761,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>153365</t>
+          <t>154088</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>173148</t>
+          <t>173138</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4776,7 +4776,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>74,61%</t>
+          <t>74,96%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -4796,12 +4796,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>316695</t>
+          <t>319434</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>343869</t>
+          <t>345302</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>77,46%</t>
+          <t>78,13%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>84,1%</t>
+          <t>84,45%</t>
         </is>
       </c>
     </row>
@@ -4839,12 +4839,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>19321</t>
+          <t>19332</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>36608</t>
+          <t>36177</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4854,12 +4854,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>17569</t>
+          <t>17436</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>33046</t>
+          <t>33475</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>41193</t>
+          <t>41039</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>64330</t>
+          <t>62741</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>15,34%</t>
         </is>
       </c>
     </row>
@@ -5069,12 +5069,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>26031</t>
+          <t>26679</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>44964</t>
+          <t>45399</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>40346</t>
+          <t>39674</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>62412</t>
+          <t>62672</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>71474</t>
+          <t>71668</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>100599</t>
+          <t>100686</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5154,7 +5154,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -5182,12 +5182,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>507738</t>
+          <t>510554</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>543449</t>
+          <t>545942</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5197,12 +5197,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>75,71%</t>
+          <t>76,13%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>81,04%</t>
+          <t>81,41%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5217,12 +5217,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>535959</t>
+          <t>534989</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>574154</t>
+          <t>573493</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>74,7%</t>
+          <t>74,56%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>80,02%</t>
+          <t>79,93%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5252,12 +5252,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1057224</t>
+          <t>1056504</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1108670</t>
+          <t>1106926</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>76,16%</t>
+          <t>76,11%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>79,87%</t>
+          <t>79,74%</t>
         </is>
       </c>
     </row>
@@ -5295,12 +5295,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>92957</t>
+          <t>92977</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>126240</t>
+          <t>125513</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5315,7 +5315,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>96195</t>
+          <t>95324</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>126511</t>
+          <t>129567</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5345,12 +5345,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>18,06%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5365,12 +5365,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>196712</t>
+          <t>200046</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>241298</t>
+          <t>244351</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5380,12 +5380,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>17,6%</t>
         </is>
       </c>
     </row>
@@ -5757,12 +5757,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2985</t>
+          <t>3027</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12679</t>
+          <t>12764</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5792,12 +5792,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4325</t>
+          <t>4371</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14489</t>
+          <t>15001</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5827,12 +5827,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>9412</t>
+          <t>9274</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>23289</t>
+          <t>22525</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5842,12 +5842,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>8,69%</t>
         </is>
       </c>
     </row>
@@ -5870,12 +5870,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>74147</t>
+          <t>73129</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>91945</t>
+          <t>91029</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>59,8%</t>
+          <t>58,98%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>74,15%</t>
+          <t>73,41%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5905,12 +5905,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>81388</t>
+          <t>80515</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>99810</t>
+          <t>99872</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>60,14%</t>
+          <t>59,49%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>73,75%</t>
+          <t>73,79%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>158924</t>
+          <t>159657</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>185135</t>
+          <t>185696</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>61,28%</t>
+          <t>61,56%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>71,39%</t>
+          <t>71,61%</t>
         </is>
       </c>
     </row>
@@ -5983,12 +5983,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>26514</t>
+          <t>27210</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>43872</t>
+          <t>44364</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>21,38%</t>
+          <t>21,94%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>35,38%</t>
+          <t>35,78%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>27582</t>
+          <t>27906</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>45555</t>
+          <t>46120</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>20,62%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>33,66%</t>
+          <t>34,08%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>58820</t>
+          <t>58540</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>84168</t>
+          <t>83305</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>22,68%</t>
+          <t>22,57%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>32,46%</t>
+          <t>32,12%</t>
         </is>
       </c>
     </row>
@@ -6213,12 +6213,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>6551</t>
+          <t>6711</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>16526</t>
+          <t>16843</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6228,12 +6228,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6248,12 +6248,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>4212</t>
+          <t>4405</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>14055</t>
+          <t>13997</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6283,12 +6283,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>12706</t>
+          <t>12897</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>25944</t>
+          <t>26537</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,57%</t>
         </is>
       </c>
     </row>
@@ -6326,12 +6326,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>141636</t>
+          <t>140754</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>159712</t>
+          <t>159364</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6341,12 +6341,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>72,84%</t>
+          <t>72,39%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>82,14%</t>
+          <t>81,96%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>149688</t>
+          <t>149580</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>168862</t>
+          <t>169239</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>71,5%</t>
+          <t>71,45%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>80,66%</t>
+          <t>80,84%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>297849</t>
+          <t>296902</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>324290</t>
+          <t>324755</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>73,76%</t>
+          <t>73,53%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>80,31%</t>
+          <t>80,42%</t>
         </is>
       </c>
     </row>
@@ -6439,12 +6439,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>25273</t>
+          <t>25250</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>41239</t>
+          <t>41927</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>21,21%</t>
+          <t>21,56%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>32612</t>
+          <t>33090</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>51055</t>
+          <t>51758</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>15,81%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>24,39%</t>
+          <t>24,72%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>62014</t>
+          <t>61755</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>87463</t>
+          <t>87825</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>15,29%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>21,75%</t>
         </is>
       </c>
     </row>
@@ -6669,12 +6669,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3556</t>
+          <t>3643</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>12546</t>
+          <t>11956</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6684,82 +6684,82 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
+          <t>8,69%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>11188</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>6939</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>18049</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>7,67%</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>4,75%</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>12,37%</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>17967</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>12543</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>25850</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>6,34%</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>4,42%</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
           <t>9,12%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>11188</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>6734</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>18082</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>7,67%</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>4,61%</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>12,39%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>17967</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>12040</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>25554</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>6,34%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>4,25%</t>
-        </is>
-      </c>
-      <c r="W12" s="2" t="inlineStr">
-        <is>
-          <t>9,01%</t>
         </is>
       </c>
     </row>
@@ -6782,12 +6782,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>87104</t>
+          <t>86898</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>104802</t>
+          <t>104027</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>63,3%</t>
+          <t>63,15%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>76,16%</t>
+          <t>75,6%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>91504</t>
+          <t>91641</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>109981</t>
+          <t>109501</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6832,12 +6832,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>62,7%</t>
+          <t>62,79%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>75,36%</t>
+          <t>75,03%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>184289</t>
+          <t>184743</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>209678</t>
+          <t>210000</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6867,12 +6867,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>64,99%</t>
+          <t>65,15%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>73,95%</t>
+          <t>74,06%</t>
         </is>
       </c>
     </row>
@@ -6895,12 +6895,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>27270</t>
+          <t>27821</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>42852</t>
+          <t>43525</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>20,22%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>31,14%</t>
+          <t>31,63%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>25811</t>
+          <t>26000</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>42354</t>
+          <t>43289</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>29,02%</t>
+          <t>29,66%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>56391</t>
+          <t>56705</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>79288</t>
+          <t>79905</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>27,96%</t>
+          <t>28,18%</t>
         </is>
       </c>
     </row>
@@ -7125,12 +7125,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2394</t>
+          <t>2387</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11201</t>
+          <t>11290</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7145,7 +7145,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7954</t>
+          <t>7973</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>19728</t>
+          <t>19722</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7175,12 +7175,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>12137</t>
+          <t>12685</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>27112</t>
+          <t>26362</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7210,12 +7210,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>6,98%</t>
         </is>
       </c>
     </row>
@@ -7238,12 +7238,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>143097</t>
+          <t>143140</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>162480</t>
+          <t>162256</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7253,12 +7253,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>74,28%</t>
+          <t>74,3%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>84,34%</t>
+          <t>84,22%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7273,12 +7273,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>132660</t>
+          <t>132317</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>151660</t>
+          <t>152647</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7288,12 +7288,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>71,72%</t>
+          <t>71,54%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>81,99%</t>
+          <t>82,53%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7308,12 +7308,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>282689</t>
+          <t>283274</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>309278</t>
+          <t>309373</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7323,12 +7323,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>74,86%</t>
+          <t>75,02%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>81,9%</t>
+          <t>81,93%</t>
         </is>
       </c>
     </row>
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>25403</t>
+          <t>25233</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>43639</t>
+          <t>43527</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7366,12 +7366,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>22,59%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7386,12 +7386,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>21220</t>
+          <t>20397</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>37917</t>
+          <t>36738</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7401,12 +7401,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>19,86%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7421,12 +7421,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>51434</t>
+          <t>50877</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>75396</t>
+          <t>74495</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7436,12 +7436,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>19,73%</t>
         </is>
       </c>
     </row>
@@ -7581,12 +7581,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>21205</t>
+          <t>22215</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>39404</t>
+          <t>39758</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7596,12 +7596,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7616,12 +7616,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>30280</t>
+          <t>31493</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>52061</t>
+          <t>53121</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7631,12 +7631,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7651,12 +7651,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>57203</t>
+          <t>57679</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>84244</t>
+          <t>84218</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7666,7 +7666,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -7694,12 +7694,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>463851</t>
+          <t>463582</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>501824</t>
+          <t>499803</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7709,12 +7709,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>71,51%</t>
+          <t>71,46%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>77,36%</t>
+          <t>77,05%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7729,12 +7729,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>476442</t>
+          <t>475281</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>514206</t>
+          <t>514934</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7744,12 +7744,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>70,52%</t>
+          <t>70,35%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>76,11%</t>
+          <t>76,22%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7764,12 +7764,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>948962</t>
+          <t>952048</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1004038</t>
+          <t>1003988</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7779,12 +7779,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>71,66%</t>
+          <t>71,89%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>75,82%</t>
+          <t>75,81%</t>
         </is>
       </c>
     </row>
@@ -7807,12 +7807,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>118194</t>
+          <t>119075</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>153281</t>
+          <t>152959</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7822,12 +7822,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>18,36%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>23,63%</t>
+          <t>23,58%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7842,12 +7842,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>121365</t>
+          <t>122331</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>157614</t>
+          <t>158757</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7857,12 +7857,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>18,11%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>23,5%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7877,12 +7877,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>251289</t>
+          <t>251407</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>300680</t>
+          <t>299076</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7897,7 +7897,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>22,58%</t>
         </is>
       </c>
     </row>
@@ -8269,12 +8269,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>490</t>
+          <t>498</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4458</t>
+          <t>4289</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8284,12 +8284,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>26,14%</t>
+          <t>25,15%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8309,7 +8309,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4220</t>
+          <t>4257</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8324,7 +8324,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>19,65%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8339,12 +8339,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1118</t>
+          <t>1150</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6439</t>
+          <t>6514</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8354,12 +8354,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>16,82%</t>
         </is>
       </c>
     </row>
@@ -8382,12 +8382,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9291</t>
+          <t>8873</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15328</t>
+          <t>15060</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8397,12 +8397,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>54,48%</t>
+          <t>52,03%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>89,88%</t>
+          <t>88,31%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8417,12 +8417,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>14461</t>
+          <t>13631</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>20281</t>
+          <t>19823</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8432,12 +8432,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>66,74%</t>
+          <t>62,92%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,61%</t>
+          <t>91,49%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8452,12 +8452,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>25913</t>
+          <t>25308</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>34056</t>
+          <t>33901</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8467,12 +8467,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>66,92%</t>
+          <t>65,36%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>87,96%</t>
+          <t>87,55%</t>
         </is>
       </c>
     </row>
@@ -8495,12 +8495,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>642</t>
+          <t>857</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6412</t>
+          <t>6817</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8510,12 +8510,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>37,6%</t>
+          <t>39,97%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8530,12 +8530,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>654</t>
+          <t>658</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6302</t>
+          <t>6209</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8545,12 +8545,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>29,09%</t>
+          <t>28,66%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8565,12 +8565,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2451</t>
+          <t>2654</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>9764</t>
+          <t>9858</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8580,12 +8580,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>25,46%</t>
         </is>
       </c>
     </row>
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1822</t>
+          <t>1636</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>9021</t>
+          <t>8730</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8740,12 +8740,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>31,14%</t>
+          <t>30,13%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8760,12 +8760,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2052</t>
+          <t>2302</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>9362</t>
+          <t>9665</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8775,12 +8775,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>19,43%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8795,12 +8795,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4860</t>
+          <t>5346</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>15169</t>
+          <t>15436</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8810,12 +8810,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>19,61%</t>
         </is>
       </c>
     </row>
@@ -8838,12 +8838,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>16241</t>
+          <t>16640</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>24492</t>
+          <t>24715</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8853,12 +8853,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>56,05%</t>
+          <t>57,43%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>84,53%</t>
+          <t>85,3%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8873,12 +8873,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>32488</t>
+          <t>32016</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>42760</t>
+          <t>42502</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8888,12 +8888,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>65,32%</t>
+          <t>64,37%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>85,97%</t>
+          <t>85,46%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8908,12 +8908,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>52594</t>
+          <t>51655</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>65319</t>
+          <t>65031</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8923,12 +8923,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>66,82%</t>
+          <t>65,63%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>82,99%</t>
+          <t>82,62%</t>
         </is>
       </c>
     </row>
@@ -8951,12 +8951,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1239</t>
+          <t>1187</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7775</t>
+          <t>7795</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8966,12 +8966,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>26,83%</t>
+          <t>26,9%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8986,12 +8986,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3520</t>
+          <t>3425</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11958</t>
+          <t>12135</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9001,12 +9001,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>24,04%</t>
+          <t>24,4%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9021,12 +9021,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6016</t>
+          <t>6321</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>16358</t>
+          <t>16605</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9036,12 +9036,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>21,1%</t>
         </is>
       </c>
     </row>
@@ -9181,12 +9181,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1226</t>
+          <t>1307</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7357</t>
+          <t>7654</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9196,12 +9196,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>28,04%</t>
+          <t>29,18%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9216,12 +9216,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>534</t>
+          <t>576</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6771</t>
+          <t>6757</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9231,12 +9231,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>21,37%</t>
+          <t>21,33%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9251,12 +9251,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2577</t>
+          <t>2797</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>10838</t>
+          <t>11806</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9266,12 +9266,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>20,38%</t>
         </is>
       </c>
     </row>
@@ -9294,12 +9294,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18879</t>
+          <t>18582</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>25010</t>
+          <t>24929</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9309,12 +9309,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>71,96%</t>
+          <t>70,82%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>95,02%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9329,12 +9329,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>14017</t>
+          <t>13418</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>25161</t>
+          <t>25156</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9344,12 +9344,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>44,24%</t>
+          <t>42,36%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>79,42%</t>
+          <t>79,41%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9364,12 +9364,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>35384</t>
+          <t>34346</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>48918</t>
+          <t>48681</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9379,12 +9379,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>61,1%</t>
+          <t>59,3%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>84,46%</t>
+          <t>84,05%</t>
         </is>
       </c>
     </row>
@@ -9442,12 +9442,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>4180</t>
+          <t>4464</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>15395</t>
+          <t>16197</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9457,12 +9457,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>14,09%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>48,6%</t>
+          <t>51,13%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9477,12 +9477,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4186</t>
+          <t>3982</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>17270</t>
+          <t>18006</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9492,12 +9492,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>29,82%</t>
+          <t>31,09%</t>
         </is>
       </c>
     </row>
@@ -9637,12 +9637,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1003</t>
+          <t>628</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6272</t>
+          <t>5562</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9652,12 +9652,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>19,83%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9672,12 +9672,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1715</t>
+          <t>1592</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8801</t>
+          <t>8529</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>30,87%</t>
+          <t>29,92%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9707,12 +9707,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3269</t>
+          <t>3546</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>12024</t>
+          <t>12201</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9722,12 +9722,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>21,26%</t>
+          <t>21,57%</t>
         </is>
       </c>
     </row>
@@ -9750,12 +9750,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>18077</t>
+          <t>18253</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>24566</t>
+          <t>24852</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9765,12 +9765,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>64,45%</t>
+          <t>65,07%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>87,58%</t>
+          <t>88,6%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9785,12 +9785,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>15222</t>
+          <t>15489</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>23804</t>
+          <t>23951</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9800,12 +9800,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>53,39%</t>
+          <t>54,33%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>83,49%</t>
+          <t>84,01%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9820,12 +9820,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>36216</t>
+          <t>35981</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>46919</t>
+          <t>46741</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9835,12 +9835,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>64,03%</t>
+          <t>63,62%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>82,96%</t>
+          <t>82,64%</t>
         </is>
       </c>
     </row>
@@ -9863,12 +9863,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1655</t>
+          <t>1339</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>7256</t>
+          <t>7111</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9878,12 +9878,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>25,87%</t>
+          <t>25,35%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9898,12 +9898,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1457</t>
+          <t>1512</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>8220</t>
+          <t>8506</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>28,83%</t>
+          <t>29,83%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9933,12 +9933,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>4396</t>
+          <t>4349</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>13339</t>
+          <t>12823</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9948,12 +9948,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>23,58%</t>
+          <t>22,67%</t>
         </is>
       </c>
     </row>
@@ -10093,12 +10093,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>7095</t>
+          <t>7330</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>17965</t>
+          <t>18001</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10108,12 +10108,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10128,12 +10128,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>8700</t>
+          <t>7637</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>20784</t>
+          <t>20142</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10143,12 +10143,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>15,31%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10163,12 +10163,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>17084</t>
+          <t>18026</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>33511</t>
+          <t>33082</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10178,12 +10178,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,27%</t>
         </is>
       </c>
     </row>
@@ -10206,12 +10206,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>70726</t>
+          <t>71288</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>84759</t>
+          <t>84744</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10221,12 +10221,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>70,5%</t>
+          <t>71,06%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>84,49%</t>
+          <t>84,48%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>85091</t>
+          <t>84853</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>104228</t>
+          <t>104410</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10256,12 +10256,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>64,66%</t>
+          <t>64,48%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>79,21%</t>
+          <t>79,34%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10276,12 +10276,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>161722</t>
+          <t>162218</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>186303</t>
+          <t>185488</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10291,12 +10291,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>69,74%</t>
+          <t>69,95%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>80,34%</t>
+          <t>79,98%</t>
         </is>
       </c>
     </row>
@@ -10319,12 +10319,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>6111</t>
+          <t>5958</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>16241</t>
+          <t>16520</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10334,12 +10334,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10354,12 +10354,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>15913</t>
+          <t>15061</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>32454</t>
+          <t>33374</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10369,12 +10369,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>24,66%</t>
+          <t>25,36%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10389,12 +10389,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>24196</t>
+          <t>24229</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>44452</t>
+          <t>43879</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10404,12 +10404,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>19,17%</t>
+          <t>18,92%</t>
         </is>
       </c>
     </row>
